--- a/OMOP Analysis/Results/Yearly/yearly_combined_summary_encounters_OMOP.xlsx
+++ b/OMOP Analysis/Results/Yearly/yearly_combined_summary_encounters_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -532,295 +532,99 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>14.85</v>
+        <v>26.41</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="F4">
-        <v>14.65</v>
+        <v>21.87</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I4">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J4">
-        <v>22900</v>
+        <v>22302</v>
       </c>
       <c r="K4">
-        <v>340113</v>
+        <v>589003</v>
       </c>
       <c r="L4">
-        <v>14.85</v>
+        <v>26.41</v>
       </c>
       <c r="M4">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N4">
-        <v>14.66</v>
+        <v>26.12</v>
       </c>
       <c r="O4">
-        <v>15.04</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>12.62</v>
+        <v>20.35</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>164</v>
+        <v>332</v>
       </c>
       <c r="F5">
-        <v>13.59</v>
+        <v>20.63</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I5">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J5">
-        <v>14172</v>
+        <v>14062</v>
       </c>
       <c r="K5">
-        <v>178832</v>
+        <v>286131</v>
       </c>
       <c r="L5">
-        <v>7.81</v>
+        <v>12.83</v>
       </c>
       <c r="M5">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="N5">
-        <v>12.39</v>
+        <v>20.01</v>
       </c>
       <c r="O5">
-        <v>12.84</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>26.49</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>346</v>
-      </c>
-      <c r="F6">
-        <v>21.87</v>
-      </c>
-      <c r="G6">
-        <v>12</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
-      </c>
-      <c r="I6">
-        <v>34</v>
-      </c>
-      <c r="J6">
-        <v>22218</v>
-      </c>
-      <c r="K6">
-        <v>588487</v>
-      </c>
-      <c r="L6">
-        <v>26.49</v>
-      </c>
-      <c r="M6">
-        <v>0.15</v>
-      </c>
-      <c r="N6">
-        <v>26.2</v>
-      </c>
-      <c r="O6">
-        <v>26.77</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>20.37</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>332</v>
-      </c>
-      <c r="F7">
-        <v>20.63</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <v>15</v>
-      </c>
-      <c r="I7">
-        <v>28</v>
-      </c>
-      <c r="J7">
-        <v>14045</v>
-      </c>
-      <c r="K7">
-        <v>286099</v>
-      </c>
-      <c r="L7">
-        <v>12.88</v>
-      </c>
-      <c r="M7">
-        <v>0.17</v>
-      </c>
-      <c r="N7">
-        <v>20.03</v>
-      </c>
-      <c r="O7">
-        <v>20.71</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>15.31</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>315</v>
-      </c>
-      <c r="F8">
-        <v>14.64</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="H8">
-        <v>11</v>
-      </c>
-      <c r="I8">
-        <v>20</v>
-      </c>
-      <c r="J8">
-        <v>22218</v>
-      </c>
-      <c r="K8">
-        <v>340113</v>
-      </c>
-      <c r="L8">
-        <v>15.31</v>
-      </c>
-      <c r="M8">
-        <v>0.1</v>
-      </c>
-      <c r="N8">
-        <v>15.12</v>
-      </c>
-      <c r="O8">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>12.73</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>164</v>
-      </c>
-      <c r="F9">
-        <v>13.59</v>
-      </c>
-      <c r="G9">
-        <v>4</v>
-      </c>
-      <c r="H9">
-        <v>9</v>
-      </c>
-      <c r="I9">
-        <v>17</v>
-      </c>
-      <c r="J9">
-        <v>14045</v>
-      </c>
-      <c r="K9">
-        <v>178832</v>
-      </c>
-      <c r="L9">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="M9">
-        <v>0.11</v>
-      </c>
-      <c r="N9">
-        <v>12.51</v>
-      </c>
-      <c r="O9">
-        <v>12.96</v>
+        <v>20.69</v>
       </c>
     </row>
   </sheetData>
